--- a/results/tables/16_final_TWFE_results.xlsx
+++ b/results/tables/16_final_TWFE_results.xlsx
@@ -425,16 +425,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.0179142524069589</v>
+        <v>-0.0171577292272654</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0106180575918961</v>
+        <v>0.0104543457635575</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.68714967421456</v>
+        <v>-1.64120544846288</v>
       </c>
       <c r="E2" t="n">
-        <v>0.166849667571445</v>
+        <v>0.176098893067961</v>
       </c>
     </row>
     <row r="3">
@@ -442,16 +442,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>0.000627041351773554</v>
+        <v>0.000623820651082471</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000252804826457595</v>
+        <v>0.000248696152958117</v>
       </c>
       <c r="D3" t="n">
-        <v>2.48033773943289</v>
+        <v>2.50836469990563</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0681864366460576</v>
+        <v>0.0661727460592482</v>
       </c>
     </row>
     <row r="4">
@@ -459,16 +459,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0558541192756409</v>
+        <v>-0.0557642436252803</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0101486915457556</v>
+        <v>0.0100674365527475</v>
       </c>
       <c r="D4" t="n">
-        <v>-5.50357837006096</v>
+        <v>-5.53907077865435</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00531563672850819</v>
+        <v>0.00519365704657689</v>
       </c>
     </row>
     <row r="5">
@@ -476,16 +476,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.000099700139084651</v>
+        <v>-0.0000680469738216597</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00025640334187266</v>
+        <v>0.000318307581787583</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.388841028188182</v>
+        <v>-0.213777420693264</v>
       </c>
       <c r="E5" t="n">
-        <v>0.717205034643977</v>
+        <v>0.841175373625743</v>
       </c>
     </row>
   </sheetData>
@@ -555,13 +555,13 @@
         <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0179142524069589</v>
+        <v>-0.0171577292272654</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0106180575918961</v>
+        <v>0.0104543457635575</v>
       </c>
       <c r="D4" t="n">
-        <v>0.166849667571445</v>
+        <v>0.176098893067961</v>
       </c>
       <c r="E4" t="n">
         <v>65</v>
@@ -616,10 +616,10 @@
         <v>16</v>
       </c>
       <c r="B4" t="n">
-        <v>0.901403158341552</v>
+        <v>0.901073293645997</v>
       </c>
       <c r="C4" t="n">
-        <v>0.513230683199479</v>
+        <v>0.511602152206083</v>
       </c>
     </row>
   </sheetData>
@@ -664,7 +664,7 @@
         <v>-0.140542314573349</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.243912696359426</v>
+        <v>-0.224133224981777</v>
       </c>
     </row>
     <row r="3">
@@ -681,7 +681,7 @@
         <v>-0.284463902291939</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1925789708053</v>
+        <v>-0.157154889642264</v>
       </c>
     </row>
     <row r="4">
@@ -698,7 +698,7 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0201407131616609</v>
+        <v>0.00277627344317959</v>
       </c>
     </row>
     <row r="5">
@@ -706,13 +706,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.243912696359426</v>
+        <v>-0.224133224981777</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1925789708053</v>
+        <v>-0.157154889642264</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0201407131616609</v>
+        <v>0.00277627344317959</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
